--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\azrfilsrv01\部門\情報ITクリエイター事業部\10_情報処理教育\50_卒業制作\00_科目指導資料\10_企画書・プロジェクト計画書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5AB196-4012-4A62-ACFC-E227B123A16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA84034-0934-4F16-B196-D22F21AF1ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="企画書" sheetId="10" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -116,6 +113,10 @@
     <rPh sb="6" eb="8">
       <t>ジョウホウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地震で被災した建造物の被害状況を文字や画像で送信し、工事が必要か診断する</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -380,6 +381,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -399,21 +415,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2266,9 +2267,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2306,9 +2307,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2341,26 +2342,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2393,26 +2377,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2596,7 +2563,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2607,7 +2574,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="13"/>
       <c r="C3" s="11"/>
     </row>
@@ -2615,16 +2582,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
+      <c r="B5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="24"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -2634,33 +2603,33 @@
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22"/>
-      <c r="B11" s="24"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
-      <c r="B13" s="25"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="14"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2671,98 +2640,98 @@
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22"/>
-      <c r="B15" s="24"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
-      <c r="B16" s="24"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="24"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="24"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="24"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="24"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="24"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="24"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="24"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="24"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="24"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="24"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="24"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
-      <c r="B33" s="25"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="14"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2773,23 +2742,23 @@
       <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="26"/>
-      <c r="B35" s="24"/>
+      <c r="A35" s="19"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26"/>
-      <c r="B36" s="24"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
-      <c r="B37" s="24"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
-      <c r="B38" s="25"/>
+      <c r="B38" s="18"/>
       <c r="C38" s="14"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2801,27 +2770,27 @@
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="24"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
-      <c r="B41" s="24"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="17"/>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22"/>
-      <c r="B42" s="24"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="17"/>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22"/>
-      <c r="B43" s="24"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="17"/>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22"/>
-      <c r="B44" s="24"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="17"/>
       <c r="C44" s="2"/>
     </row>
   </sheetData>
@@ -2840,6 +2809,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3046,28 +3035,17 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3079,12 +3057,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA84034-0934-4F16-B196-D22F21AF1ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2D4A32-D60C-40A7-9B18-7C271E4D91F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2809,26 +2809,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3035,28 +3015,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3073,4 +3052,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2D4A32-D60C-40A7-9B18-7C271E4D91F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BE6D7D-AD6D-47D6-A3D2-45385149C7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -117,6 +117,30 @@
   </si>
   <si>
     <t>地震で被災した建造物の被害状況を文字や画像で送信し、工事が必要か診断する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先日発生した令和8年熊本地震により多くの家屋が被害を受けた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判断するというものであり、建築物内部の被害については考慮されていない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その後行政が被災建築物応急危険度判定を実施したが、その判定方法は建築物の外観を元に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのため、建築物内部の被害状況を把握するためには専門家に依頼する必要があり、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手間と費用がかかる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そこで個人が写真を撮り、質問に答えるだけで被害状況の目安を把握できるシステムが必要だと考えた。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -335,7 +359,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,37 +408,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2563,7 +2599,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2574,7 +2610,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="13"/>
       <c r="C3" s="11"/>
     </row>
@@ -2582,18 +2618,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
@@ -2603,34 +2639,46 @@
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="23"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="14"/>
+      <c r="A13" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="25"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
@@ -2641,97 +2689,97 @@
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
-      <c r="B16" s="17"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
-      <c r="B18" s="17"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
-      <c r="B20" s="17"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
-      <c r="B22" s="17"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
-      <c r="B24" s="17"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
-      <c r="B25" s="17"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
-      <c r="B26" s="17"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
-      <c r="B27" s="17"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
-      <c r="B28" s="17"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
-      <c r="B32" s="17"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
-      <c r="B33" s="18"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="14"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2742,23 +2790,23 @@
       <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="17"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="17"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
-      <c r="B37" s="17"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
-      <c r="B38" s="18"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="14"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2770,34 +2818,40 @@
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12"/>
-      <c r="B40" s="17"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="2"/>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
-      <c r="B41" s="17"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
-      <c r="B42" s="17"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
-      <c r="B43" s="17"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
-      <c r="B44" s="17"/>
+      <c r="B44" s="16"/>
       <c r="C44" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2809,6 +2863,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3015,27 +3089,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3052,25 +3127,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BE6D7D-AD6D-47D6-A3D2-45385149C7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0007A016-44E0-4637-8AF9-B6B9702A2E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="企画書" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">企画書!$A$1:$C$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">企画書!$A$1:$C$46</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -141,6 +141,82 @@
   </si>
   <si>
     <t>そこで個人が写真を撮り、質問に答えるだけで被害状況の目安を把握できるシステムが必要だと考えた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1．被害状況写真の撮影・登録機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災した建物内部の写真を撮影し、システムへ登録できる機能。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数の写真を登録することで、建物内のさまざまな被害箇所を記録できる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2．AIによる被害状況分析機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録された写真をAIが分析し、壁・床・天井などの被害状況や被害の程度を</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判断するための目安を提示する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3．修理費用の目安提示機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIによる被害状況の分析結果をもとに、必要となる修理・復旧にかかる費用の目安を提示する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．罹災証明書の申請案内機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が罹災証明書を申請する際に必要となる手続きや申請方法、必要書類などの情報を案内する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5．修理業者の情報提示機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況や修理内容に応じて、利用可能な修理業者の情報を提示し、業者探しを支援する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6．被災後の対応案内機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況に応じて、修理や各種申請など、被災後に必要となる対応を順番に案内することで、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が次に何をすべきかを分かりやすくする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7．被害状況・分析履歴機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去に登録した被害状況の写真やAIによる分析結果を履歴として保存し、後から確認できる機能。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、「ドアや窓が正常に開閉できるか」「建物から異音がするか」などの質問に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者が回答することで、画像だけでは判断できない情報も収集する。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -359,98 +435,104 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1112,13 +1194,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1178,13 +1260,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1244,13 +1326,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1310,13 +1392,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1367,13 +1449,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1424,13 +1506,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1490,13 +1572,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1556,13 +1638,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1622,13 +1704,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1679,13 +1761,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1736,13 +1818,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1802,13 +1884,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1868,13 +1950,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1934,13 +2016,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1991,13 +2073,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2048,13 +2130,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2105,13 +2187,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2171,13 +2253,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2237,13 +2319,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2589,7 +2671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -2599,250 +2681,328 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="11"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="25"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="2"/>
+      <c r="A25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="2"/>
+      <c r="A26" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="2"/>
+      <c r="A27" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="2"/>
+      <c r="A28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="2"/>
+      <c r="A29" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="2"/>
+      <c r="A31" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="14"/>
-    </row>
-    <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
+    </row>
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="12"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="25"/>
+    </row>
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+    </row>
+    <row r="36" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
-    </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="2"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="14"/>
-    </row>
-    <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+    </row>
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="12"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="25"/>
+    </row>
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="27"/>
+    </row>
+    <row r="41" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="5"/>
-    </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="4"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="2"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="31"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="2"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="25"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="2"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
+    </row>
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="12"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="25"/>
+    </row>
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="12"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="39">
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
@@ -2863,26 +3023,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3089,28 +3229,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3127,4 +3266,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0007A016-44E0-4637-8AF9-B6B9702A2E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64B01A6-30D4-4853-B4A7-1B592628DB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -132,91 +132,181 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>そこで個人が写真を撮り、質問に答えるだけで被害状況の目安を把握できるシステムが必要だと考えた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1．被害状況写真の撮影・登録機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災した建物内部の写真を撮影し、システムへ登録できる機能。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数の写真を登録することで、建物内のさまざまな被害箇所を記録できる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2．AIによる被害状況分析機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録された写真をAIが分析し、壁・床・天井などの被害状況や被害の程度を</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判断するための目安を提示する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3．修理費用の目安提示機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIによる被害状況の分析結果をもとに、必要となる修理・復旧にかかる費用の目安を提示する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．罹災証明書の申請案内機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が罹災証明書を申請する際に必要となる手続きや申請方法、必要書類などの情報を案内する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5．修理業者の情報提示機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況や修理内容に応じて、利用可能な修理業者の情報を提示し、業者探しを支援する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6．被災後の対応案内機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況に応じて、修理や各種申請など、被災後に必要となる対応を順番に案内することで、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が次に何をすべきかを分かりやすくする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7．被害状況・分析履歴機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去に登録した被害状況の写真やAIによる分析結果を履歴として保存し、後から確認できる機能。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>また、「ドアや窓が正常に開閉できるか」「建物から異音がするか」などの質問に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者が回答することで、画像だけでは判断できない情報も収集する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提案先：建物調査を実施している企業、修理業者</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ギョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行政向けの類似システムはあったが、一般向けのものは無かった</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ルイジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>イッパンム</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手間と費用がかかり、また悪徳業者に不当な契約をされるリスクがある。</t>
+    <rPh sb="12" eb="14">
+      <t>アクトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ギョウシャ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フトウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>そのため、建築物内部の被害状況を把握するためには専門家に依頼する必要があり、</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>手間と費用がかかる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そこで個人が写真を撮り、質問に答えるだけで被害状況の目安を把握できるシステムが必要だと考えた。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1．被害状況写真の撮影・登録機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災した建物内部の写真を撮影し、システムへ登録できる機能。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>複数の写真を登録することで、建物内のさまざまな被害箇所を記録できる。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2．AIによる被害状況分析機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録された写真をAIが分析し、壁・床・天井などの被害状況や被害の程度を</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>判断するための目安を提示する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3．修理費用の目安提示機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>AIによる被害状況の分析結果をもとに、必要となる修理・復旧にかかる費用の目安を提示する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4．罹災証明書の申請案内機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災者が罹災証明書を申請する際に必要となる手続きや申請方法、必要書類などの情報を案内する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5．修理業者の情報提示機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況や修理内容に応じて、利用可能な修理業者の情報を提示し、業者探しを支援する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>6．被災後の対応案内機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況に応じて、修理や各種申請など、被災後に必要となる対応を順番に案内することで、</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災者が次に何をすべきかを分かりやすくする。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7．被害状況・分析履歴機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>過去に登録した被害状況の写真やAIによる分析結果を履歴として保存し、後から確認できる機能。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>また、「ドアや窓が正常に開閉できるか」「建物から異音がするか」などの質問に</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>利用者が回答することで、画像だけでは判断できない情報も収集する。</t>
+    <rPh sb="24" eb="27">
+      <t>センモンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイガイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シツナイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ジギョウシャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>カンリシャ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -435,7 +525,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -475,13 +565,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -497,42 +620,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2681,7 +2768,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2692,7 +2779,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="11"/>
       <c r="C3" s="10"/>
     </row>
@@ -2700,18 +2787,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2724,43 +2811,43 @@
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
+        <v>35</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2771,146 +2858,146 @@
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="14"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="14"/>
+        <v>31</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="25"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="25"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
     </row>
     <row r="36" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
@@ -2920,24 +3007,28 @@
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="31"/>
+      <c r="A37" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="23"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="25"/>
+      <c r="A38" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
     </row>
     <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="25"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="20"/>
     </row>
     <row r="41" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
@@ -2947,32 +3038,57 @@
       <c r="C41" s="4"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="31"/>
+      <c r="A42" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="23"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="25"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
     </row>
     <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="25"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
     </row>
     <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="25"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
@@ -2989,29 +3105,6 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3023,6 +3116,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3229,27 +3342,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3266,25 +3380,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64B01A6-30D4-4853-B4A7-1B592628DB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8AF815-1889-4531-95FA-C5132CD8BF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="企画書" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">企画書!$A$1:$C$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">企画書!$A$1:$C$44</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -234,25 +234,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>行政向けの類似システムはあったが、一般向けのものは無かった</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウセイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ルイジ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>イッパンム</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>手間と費用がかかり、また悪徳業者に不当な契約をされるリスクがある。</t>
     <rPh sb="12" eb="14">
       <t>アクトク</t>
@@ -307,6 +288,51 @@
     <rPh sb="31" eb="34">
       <t>カンリシャ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行政向けには建物内部の被害状況を確認する類似システムが存在するが、</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ルイジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一般向けのシステムは少ない。また、近年では住宅の点検を装った詐欺も発生している。</t>
+    <rPh sb="0" eb="3">
+      <t>イッパンム</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうした背景から、利用者自身が自宅内部の状況を確認できるシステムが必要だと考えた。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -525,7 +551,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -565,46 +591,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +613,42 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1281,13 +1310,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1347,13 +1376,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1413,13 +1442,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1479,13 +1508,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1536,13 +1565,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1593,13 +1622,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1659,13 +1688,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1725,13 +1754,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1791,13 +1820,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1848,13 +1877,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1905,13 +1934,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1971,13 +2000,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2037,13 +2066,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2103,13 +2132,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2160,13 +2189,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2217,13 +2246,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2274,13 +2303,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2340,13 +2369,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2406,13 +2435,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2758,7 +2787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -2768,7 +2797,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2779,7 +2808,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="11"/>
       <c r="C3" s="10"/>
     </row>
@@ -2787,18 +2816,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2811,43 +2840,43 @@
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
+        <v>34</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
+        <v>33</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2860,212 +2889,234 @@
       <c r="A15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-    </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
+    </row>
+    <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20"/>
-    </row>
-    <row r="36" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
+      <c r="A35" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
+    </row>
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="28"/>
+    </row>
+    <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-    </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-    </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="20"/>
-    </row>
-    <row r="41" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
+    </row>
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="25"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
+      <c r="A42" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="32"/>
+      <c r="C42" s="14"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-    </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
-    </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="37">
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
@@ -3075,36 +3126,6 @@
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3116,26 +3137,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3342,28 +3343,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3380,4 +3380,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8AF815-1889-4531-95FA-C5132CD8BF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B89E8D6-EAFA-4CDF-B105-9F59E0703A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -551,7 +551,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -588,6 +588,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -597,7 +600,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -613,42 +646,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2797,7 +2794,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2808,7 +2805,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="11"/>
       <c r="C3" s="10"/>
     </row>
@@ -2816,18 +2813,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2840,43 +2837,43 @@
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2889,134 +2886,134 @@
       <c r="A15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="16"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="16"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="25"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="16"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="16"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="16"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="16"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="16"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="16"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="16"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="16"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -3026,28 +3023,28 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="16"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="25"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="16"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -3060,35 +3057,56 @@
       <c r="A40" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="25"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="16"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="32"/>
-      <c r="C42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="15"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A44:C44"/>
@@ -3105,27 +3123,6 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3137,6 +3134,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3343,27 +3360,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3380,25 +3398,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/10_企画書.xlsx
+++ b/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B89E8D6-EAFA-4CDF-B105-9F59E0703A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E4DD7E-9389-4B60-86D8-23904A8F0B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -333,6 +333,10 @@
   </si>
   <si>
     <t>こうした背景から、利用者自身が自宅内部の状況を確認できるシステムが必要だと考えた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tanouesoftware</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -588,9 +592,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -600,37 +601,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -646,6 +617,39 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2794,7 +2798,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2805,26 +2809,30 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="10">
+        <v>46283</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2837,43 +2845,43 @@
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2886,134 +2894,134 @@
       <c r="A15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="16"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="16"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="16"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="16"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="16"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="16"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="16"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="16"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="16"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="16"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="16"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="16"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="16"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="16"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -3023,28 +3031,28 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="16"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="16"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="28"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -3057,56 +3065,35 @@
       <c r="A40" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="16"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="25"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="15"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="16"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A44:C44"/>
@@ -3123,6 +3110,27 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3134,26 +3142,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3360,28 +3348,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3398,4 +3385,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>